--- a/slides/board_number.xlsx
+++ b/slides/board_number.xlsx
@@ -441,12 +441,8 @@
           <t>Kalpa Health ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â· Brief A ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â· Group 6</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -467,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>tests on cleaned booking records after the documented booking and person identity rules</t>
+          <t>validated booking test lines after the documented IITGN validation and identity rules</t>
         </is>
       </c>
     </row>
@@ -478,7 +474,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>452933</v>
+        <v>455383</v>
       </c>
     </row>
     <row r="6">
@@ -488,7 +484,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>431261</v>
+        <v>433611</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +507,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>H1 2025 baseline: 431,261 tests</t>
+          <t>H1 2025 baseline: 433,611 test lines</t>
         </is>
       </c>
     </row>
@@ -523,7 +519,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>H1 2026 test volume increased 5.0% versus H1 2025, driven by more people and more tests per visit despite slightly fewer visits per person.</t>
+          <t>H1 2026 test volume increased 5.0% versus H1 2025, with more people and more test lines per visit despite slightly fewer visits per person.</t>
         </is>
       </c>
     </row>
@@ -535,7 +531,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>The result depends on the documented person identity rule and complete H1 period coverage.</t>
+          <t>This is a descriptive booking-line measure, not proof of attended or performed tests; it depends on the person rule and complete H1 coverage.</t>
         </is>
       </c>
     </row>
